--- a/youzi/宁波解放南/index.xlsx
+++ b/youzi/宁波解放南/index.xlsx
@@ -51,12 +51,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBCE3C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -81,13 +99,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBCE3C5"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,79 +285,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -189,67 +381,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -261,13 +447,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,187 +507,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
+        <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -471,133 +525,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77984"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77984"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1914,7 +1914,7 @@
       <c r="C2" t="str">
         <v>600714</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="3" t="str">
         <v>净买: 735.89万</v>
       </c>
       <c r="E2">
@@ -1929,37 +1929,37 @@
       <c r="H2">
         <v>-4.48</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="4">
         <v>-5.78</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="6">
         <v>-1.54</v>
       </c>
       <c r="K2" s="10">
         <v>-11.35</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="11">
         <v>-11.2</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="5">
         <v>-13.91</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="7">
         <v>-13.47</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="12">
         <v>-10.47</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="13">
         <v>-10.54</v>
       </c>
       <c r="Q2" s="1">
         <v>-11.2</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="8">
         <v>-11.64</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="9">
         <v>-13.4</v>
       </c>
       <c r="T2" s="2">
@@ -1976,7 +1976,7 @@
       <c r="C3" t="str">
         <v>688593</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="16" t="str">
         <v>净卖: -1079.85万</v>
       </c>
       <c r="E3">
@@ -1991,40 +1991,40 @@
       <c r="H3">
         <v>-0.06</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="22">
         <v>20.07</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="14">
         <v>35.34</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="24">
         <v>35.22</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="25">
         <v>46.33</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="26">
         <v>43.45</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N3" s="17">
         <v>51.86</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="18">
         <v>52.76</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="19">
         <v>39.24</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="20">
         <v>39.12</v>
       </c>
       <c r="R3" s="23">
         <v>39.48</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="15">
         <v>35.58</v>
       </c>
-      <c r="T3" s="22">
+      <c r="T3" s="21">
         <v>86.72</v>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       <c r="C4" t="str">
         <v>601500</v>
       </c>
-      <c r="D4" s="37" t="str">
+      <c r="D4" s="29" t="str">
         <v>净买: 1639.55万</v>
       </c>
       <c r="E4">
@@ -2053,40 +2053,40 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="30">
         <v>10.09</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="35">
         <v>10.33</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="36">
         <v>8.22</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="31">
         <v>10.56</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="27">
         <v>13.15</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="28">
         <v>12.91</v>
       </c>
-      <c r="O4" s="34">
+      <c r="O4" s="32">
         <v>12.44</v>
       </c>
-      <c r="P4" s="38">
+      <c r="P4" s="33">
         <v>8.92</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="37">
         <v>7.04</v>
       </c>
-      <c r="R4" s="39">
+      <c r="R4" s="34">
         <v>9.15</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="38">
         <v>12.44</v>
       </c>
-      <c r="T4" s="27">
+      <c r="T4" s="39">
         <v>-0.94</v>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       <c r="C5" t="str">
         <v>600337</v>
       </c>
-      <c r="D5" s="49" t="str">
+      <c r="D5" s="48" t="str">
         <v>净买: 387.19万</v>
       </c>
       <c r="E5">
@@ -2115,40 +2115,40 @@
       <c r="H5">
         <v>9.92</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="42">
         <v>0</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="52">
         <v>10.05</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="43">
         <v>-1.03</v>
       </c>
-      <c r="L5" s="50">
+      <c r="L5" s="46">
         <v>-3.61</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="44">
         <v>-12.37</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="45">
         <v>-11.6</v>
       </c>
-      <c r="O5" s="51">
+      <c r="O5" s="49">
         <v>-20.36</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="47">
         <v>-26.8</v>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="50">
         <v>-19.59</v>
       </c>
-      <c r="R5" s="44">
+      <c r="R5" s="40">
         <v>-26.29</v>
       </c>
-      <c r="S5" s="45">
+      <c r="S5" s="51">
         <v>-26.03</v>
       </c>
-      <c r="T5" s="52">
+      <c r="T5" s="41">
         <v>-11.6</v>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       <c r="C6" t="str">
         <v>603718</v>
       </c>
-      <c r="D6" s="64" t="str">
+      <c r="D6" s="57" t="str">
         <v>净卖: -161.85万</v>
       </c>
       <c r="E6">
@@ -2177,40 +2177,40 @@
       <c r="H6">
         <v>-9.93</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="64">
         <v>0</v>
       </c>
-      <c r="J6" s="65">
+      <c r="J6" s="58">
         <v>1.9</v>
       </c>
-      <c r="K6" s="56">
+      <c r="K6" s="61">
         <v>-0.76</v>
       </c>
-      <c r="L6" s="57">
+      <c r="L6" s="62">
         <v>1.9</v>
       </c>
-      <c r="M6" s="55">
+      <c r="M6" s="63">
         <v>3.23</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="59">
         <v>2.66</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="53">
         <v>0.19</v>
       </c>
-      <c r="P6" s="60">
+      <c r="P6" s="65">
         <v>-6.84</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="54">
         <v>-8.75</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="55">
         <v>-5.51</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="56">
         <v>-5.32</v>
       </c>
-      <c r="T6" s="63">
+      <c r="T6" s="60">
         <v>-18.06</v>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       <c r="C7" t="str">
         <v>002542</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="68" t="str">
         <v>净买: 684.27万</v>
       </c>
       <c r="E7">
@@ -2239,16 +2239,16 @@
       <c r="H7">
         <v>-4.24</v>
       </c>
-      <c r="I7" s="68">
+      <c r="I7" s="69">
         <v>-4.42</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="70">
         <v>-7.52</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="71">
         <v>-10.18</v>
       </c>
-      <c r="L7" s="71">
+      <c r="L7" s="66">
         <v>-9.29</v>
       </c>
       <c r="M7" t="str"/>
@@ -2258,7 +2258,7 @@
       <c r="Q7" t="str"/>
       <c r="R7" t="str"/>
       <c r="S7" t="str"/>
-      <c r="T7" s="66">
+      <c r="T7" s="67">
         <v>-9.29</v>
       </c>
     </row>
@@ -2321,40 +2321,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="74">
+      <c r="I9" s="77">
         <v>33.33</v>
       </c>
-      <c r="J9" s="78">
+      <c r="J9" s="72">
         <v>66.67</v>
       </c>
-      <c r="K9" s="76">
+      <c r="K9" s="80">
         <v>33.33</v>
       </c>
-      <c r="L9" s="79">
+      <c r="L9" s="78">
         <v>50</v>
       </c>
-      <c r="M9" s="82">
+      <c r="M9" s="73">
         <v>60</v>
       </c>
-      <c r="N9" s="77">
+      <c r="N9" s="74">
         <v>60</v>
       </c>
-      <c r="O9" s="83">
+      <c r="O9" s="75">
         <v>60</v>
       </c>
-      <c r="P9" s="80">
+      <c r="P9" s="81">
         <v>40</v>
       </c>
-      <c r="Q9" s="75">
+      <c r="Q9" s="82">
         <v>40</v>
       </c>
-      <c r="R9" s="72">
+      <c r="R9" s="76">
         <v>40</v>
       </c>
-      <c r="S9" s="81">
+      <c r="S9" s="79">
         <v>40</v>
       </c>
-      <c r="T9" s="73">
+      <c r="T9" s="83">
         <v>33.33</v>
       </c>
     </row>
@@ -2369,40 +2369,40 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="94">
+      <c r="I10" s="93">
         <v>3.33</v>
       </c>
-      <c r="J10" s="89">
+      <c r="J10" s="91">
         <v>8.09</v>
       </c>
-      <c r="K10" s="86">
+      <c r="K10" s="94">
         <v>3.35</v>
       </c>
-      <c r="L10" s="91">
+      <c r="L10" s="92">
         <v>5.78</v>
       </c>
-      <c r="M10" s="87">
+      <c r="M10" s="90">
         <v>6.71</v>
       </c>
-      <c r="N10" s="95">
+      <c r="N10" s="86">
         <v>8.47</v>
       </c>
-      <c r="O10" s="84">
+      <c r="O10" s="95">
         <v>6.91</v>
       </c>
-      <c r="P10" s="88">
+      <c r="P10" s="84">
         <v>0.8</v>
       </c>
-      <c r="Q10" s="92">
+      <c r="Q10" s="87">
         <v>1.32</v>
       </c>
-      <c r="R10" s="93">
+      <c r="R10" s="88">
         <v>1.04</v>
       </c>
-      <c r="S10" s="90">
+      <c r="S10" s="85">
         <v>0.65</v>
       </c>
-      <c r="T10" s="85">
+      <c r="T10" s="89">
         <v>13.2</v>
       </c>
     </row>

--- a/youzi/宁波解放南/index.xlsx
+++ b/youzi/宁波解放南/index.xlsx
@@ -45,7 +45,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,7 +75,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
+        <fgColor rgb="FFBCE3C5"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,12 +87,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBCE3C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -87,6 +99,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -99,6 +117,162 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -117,13 +291,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,73 +369,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -213,73 +453,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -291,85 +483,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -381,61 +507,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -447,19 +537,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -471,67 +555,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -543,61 +585,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE77984"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF3BDC2"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77984"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1914,7 +1914,7 @@
       <c r="C2" t="str">
         <v>600714</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="6" t="str">
         <v>净买: 735.89万</v>
       </c>
       <c r="E2">
@@ -1929,22 +1929,22 @@
       <c r="H2">
         <v>-4.48</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="3">
         <v>-5.78</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="7">
         <v>-1.54</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="8">
         <v>-11.35</v>
       </c>
-      <c r="L2" s="11">
+      <c r="L2" s="4">
         <v>-11.2</v>
       </c>
       <c r="M2" s="5">
         <v>-13.91</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="9">
         <v>-13.47</v>
       </c>
       <c r="O2" s="12">
@@ -1956,13 +1956,13 @@
       <c r="Q2" s="1">
         <v>-11.2</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="10">
         <v>-11.64</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="2">
         <v>-13.4</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="11">
         <v>32.36</v>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       <c r="C3" t="str">
         <v>688593</v>
       </c>
-      <c r="D3" s="16" t="str">
+      <c r="D3" s="22" t="str">
         <v>净卖: -1079.85万</v>
       </c>
       <c r="E3">
@@ -1991,40 +1991,40 @@
       <c r="H3">
         <v>-0.06</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="23">
         <v>20.07</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="24">
         <v>35.34</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="25">
         <v>35.22</v>
       </c>
-      <c r="L3" s="25">
+      <c r="L3" s="19">
         <v>46.33</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="16">
         <v>43.45</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="26">
         <v>51.86</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="14">
         <v>52.76</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="20">
         <v>39.24</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="15">
         <v>39.12</v>
       </c>
-      <c r="R3" s="23">
+      <c r="R3" s="17">
         <v>39.48</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="21">
         <v>35.58</v>
       </c>
-      <c r="T3" s="21">
+      <c r="T3" s="18">
         <v>86.72</v>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       <c r="C4" t="str">
         <v>601500</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="34" t="str">
         <v>净买: 1639.55万</v>
       </c>
       <c r="E4">
@@ -2053,40 +2053,40 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="35">
         <v>10.09</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="28">
         <v>10.33</v>
       </c>
       <c r="K4" s="36">
         <v>8.22</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="29">
         <v>10.56</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="39">
         <v>13.15</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="30">
         <v>12.91</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="31">
         <v>12.44</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="27">
         <v>8.92</v>
       </c>
       <c r="Q4" s="37">
         <v>7.04</v>
       </c>
-      <c r="R4" s="34">
+      <c r="R4" s="32">
         <v>9.15</v>
       </c>
       <c r="S4" s="38">
         <v>12.44</v>
       </c>
-      <c r="T4" s="39">
+      <c r="T4" s="33">
         <v>-0.94</v>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       <c r="C5" t="str">
         <v>600337</v>
       </c>
-      <c r="D5" s="48" t="str">
+      <c r="D5" s="45" t="str">
         <v>净买: 387.19万</v>
       </c>
       <c r="E5">
@@ -2115,40 +2115,40 @@
       <c r="H5">
         <v>9.92</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="49">
         <v>0</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5" s="50">
         <v>10.05</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="51">
         <v>-1.03</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="52">
         <v>-3.61</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="41">
         <v>-12.37</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="40">
         <v>-11.6</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="47">
         <v>-20.36</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="42">
         <v>-26.8</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="43">
         <v>-19.59</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="48">
         <v>-26.29</v>
       </c>
-      <c r="S5" s="51">
+      <c r="S5" s="46">
         <v>-26.03</v>
       </c>
-      <c r="T5" s="41">
+      <c r="T5" s="44">
         <v>-11.6</v>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       <c r="C6" t="str">
         <v>603718</v>
       </c>
-      <c r="D6" s="57" t="str">
+      <c r="D6" s="55" t="str">
         <v>净卖: -161.85万</v>
       </c>
       <c r="E6">
@@ -2177,40 +2177,40 @@
       <c r="H6">
         <v>-9.93</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="59">
         <v>0</v>
       </c>
-      <c r="J6" s="58">
+      <c r="J6" s="62">
         <v>1.9</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="60">
         <v>-0.76</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="56">
         <v>1.9</v>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="57">
         <v>3.23</v>
       </c>
-      <c r="N6" s="59">
+      <c r="N6" s="63">
         <v>2.66</v>
       </c>
-      <c r="O6" s="53">
+      <c r="O6" s="61">
         <v>0.19</v>
       </c>
-      <c r="P6" s="65">
+      <c r="P6" s="53">
         <v>-6.84</v>
       </c>
-      <c r="Q6" s="54">
+      <c r="Q6" s="58">
         <v>-8.75</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="54">
         <v>-5.51</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="64">
         <v>-5.32</v>
       </c>
-      <c r="T6" s="60">
+      <c r="T6" s="65">
         <v>-18.06</v>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       <c r="C7" t="str">
         <v>002542</v>
       </c>
-      <c r="D7" s="68" t="str">
+      <c r="D7" s="69" t="str">
         <v>净买: 684.27万</v>
       </c>
       <c r="E7">
@@ -2239,16 +2239,16 @@
       <c r="H7">
         <v>-4.24</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="70">
         <v>-4.42</v>
       </c>
-      <c r="J7" s="70">
+      <c r="J7" s="71">
         <v>-7.52</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="66">
         <v>-10.18</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="67">
         <v>-9.29</v>
       </c>
       <c r="M7" t="str"/>
@@ -2258,7 +2258,7 @@
       <c r="Q7" t="str"/>
       <c r="R7" t="str"/>
       <c r="S7" t="str"/>
-      <c r="T7" s="67">
+      <c r="T7" s="68">
         <v>-9.29</v>
       </c>
     </row>
@@ -2321,40 +2321,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="77">
+      <c r="I9" s="81">
         <v>33.33</v>
       </c>
-      <c r="J9" s="72">
+      <c r="J9" s="82">
         <v>66.67</v>
       </c>
-      <c r="K9" s="80">
+      <c r="K9" s="77">
         <v>33.33</v>
       </c>
-      <c r="L9" s="78">
+      <c r="L9" s="74">
         <v>50</v>
       </c>
-      <c r="M9" s="73">
+      <c r="M9" s="83">
         <v>60</v>
       </c>
-      <c r="N9" s="74">
+      <c r="N9" s="75">
         <v>60</v>
       </c>
-      <c r="O9" s="75">
+      <c r="O9" s="72">
         <v>60</v>
       </c>
-      <c r="P9" s="81">
+      <c r="P9" s="78">
         <v>40</v>
       </c>
-      <c r="Q9" s="82">
+      <c r="Q9" s="73">
         <v>40</v>
       </c>
-      <c r="R9" s="76">
+      <c r="R9" s="80">
         <v>40</v>
       </c>
       <c r="S9" s="79">
         <v>40</v>
       </c>
-      <c r="T9" s="83">
+      <c r="T9" s="76">
         <v>33.33</v>
       </c>
     </row>
@@ -2369,37 +2369,37 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="93">
+      <c r="I10" s="94">
         <v>3.33</v>
       </c>
-      <c r="J10" s="91">
+      <c r="J10" s="88">
         <v>8.09</v>
       </c>
-      <c r="K10" s="94">
+      <c r="K10" s="86">
         <v>3.35</v>
       </c>
-      <c r="L10" s="92">
+      <c r="L10" s="95">
         <v>5.78</v>
       </c>
-      <c r="M10" s="90">
+      <c r="M10" s="84">
         <v>6.71</v>
       </c>
-      <c r="N10" s="86">
+      <c r="N10" s="85">
         <v>8.47</v>
       </c>
-      <c r="O10" s="95">
+      <c r="O10" s="90">
         <v>6.91</v>
       </c>
-      <c r="P10" s="84">
+      <c r="P10" s="91">
         <v>0.8</v>
       </c>
-      <c r="Q10" s="87">
+      <c r="Q10" s="92">
         <v>1.32</v>
       </c>
-      <c r="R10" s="88">
+      <c r="R10" s="87">
         <v>1.04</v>
       </c>
-      <c r="S10" s="85">
+      <c r="S10" s="93">
         <v>0.65</v>
       </c>
       <c r="T10" s="89">

--- a/youzi/宁波解放南/index.xlsx
+++ b/youzi/宁波解放南/index.xlsx
@@ -45,12 +45,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBCE3C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF259D41"/>
         <bgColor/>
       </patternFill>
@@ -69,13 +105,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBCE3C5"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,18 +291,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -117,49 +327,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -171,67 +369,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,31 +447,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,25 +465,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -309,139 +489,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
+        <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -453,13 +507,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -471,55 +537,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -531,31 +561,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -591,19 +597,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1914,7 +1914,7 @@
       <c r="C2" t="str">
         <v>600714</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="D2" s="2" t="str">
         <v>净买: 735.89万</v>
       </c>
       <c r="E2">
@@ -1929,25 +1929,25 @@
       <c r="H2">
         <v>-4.48</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="9">
         <v>-5.78</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="6">
         <v>-1.54</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="7">
         <v>-11.35</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="10">
         <v>-11.2</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="12">
         <v>-13.91</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="3">
         <v>-13.47</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="4">
         <v>-10.47</v>
       </c>
       <c r="P2" s="13">
@@ -1956,14 +1956,14 @@
       <c r="Q2" s="1">
         <v>-11.2</v>
       </c>
-      <c r="R2" s="10">
+      <c r="R2" s="11">
         <v>-11.64</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="8">
         <v>-13.4</v>
       </c>
-      <c r="T2" s="11">
-        <v>32.36</v>
+      <c r="T2" s="5">
+        <v>38.21</v>
       </c>
     </row>
     <row r="3">
@@ -1976,7 +1976,7 @@
       <c r="C3" t="str">
         <v>688593</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="21" t="str">
         <v>净卖: -1079.85万</v>
       </c>
       <c r="E3">
@@ -1991,41 +1991,41 @@
       <c r="H3">
         <v>-0.06</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="15">
         <v>20.07</v>
       </c>
-      <c r="J3" s="24">
+      <c r="J3" s="25">
         <v>35.34</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="16">
         <v>35.22</v>
       </c>
       <c r="L3" s="19">
         <v>46.33</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="22">
         <v>43.45</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="17">
         <v>51.86</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="23">
         <v>52.76</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="26">
         <v>39.24</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="14">
         <v>39.12</v>
       </c>
-      <c r="R3" s="17">
+      <c r="R3" s="20">
         <v>39.48</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="24">
         <v>35.58</v>
       </c>
       <c r="T3" s="18">
-        <v>86.72</v>
+        <v>92.79</v>
       </c>
     </row>
     <row r="4">
@@ -2038,7 +2038,7 @@
       <c r="C4" t="str">
         <v>601500</v>
       </c>
-      <c r="D4" s="34" t="str">
+      <c r="D4" s="31" t="str">
         <v>净买: 1639.55万</v>
       </c>
       <c r="E4">
@@ -2053,40 +2053,40 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="38">
         <v>10.09</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="27">
         <v>10.33</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="28">
         <v>8.22</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="32">
         <v>10.56</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="33">
         <v>13.15</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="36">
         <v>12.91</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="29">
         <v>12.44</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="34">
         <v>8.92</v>
       </c>
       <c r="Q4" s="37">
         <v>7.04</v>
       </c>
-      <c r="R4" s="32">
+      <c r="R4" s="39">
         <v>9.15</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="30">
         <v>12.44</v>
       </c>
-      <c r="T4" s="33">
+      <c r="T4" s="35">
         <v>-0.94</v>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       <c r="C5" t="str">
         <v>600337</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="43" t="str">
         <v>净买: 387.19万</v>
       </c>
       <c r="E5">
@@ -2118,38 +2118,38 @@
       <c r="I5" s="49">
         <v>0</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="44">
         <v>10.05</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="40">
         <v>-1.03</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="45">
         <v>-3.61</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="50">
         <v>-12.37</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="51">
         <v>-11.6</v>
       </c>
-      <c r="O5" s="47">
+      <c r="O5" s="46">
         <v>-20.36</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="47">
         <v>-26.8</v>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="52">
         <v>-19.59</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="41">
         <v>-26.29</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="48">
         <v>-26.03</v>
       </c>
-      <c r="T5" s="44">
-        <v>-11.6</v>
+      <c r="T5" s="42">
+        <v>-12.37</v>
       </c>
     </row>
     <row r="6">
@@ -2177,41 +2177,41 @@
       <c r="H6">
         <v>-9.93</v>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="56">
         <v>0</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="57">
         <v>1.9</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="58">
         <v>-0.76</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="64">
         <v>1.9</v>
       </c>
-      <c r="M6" s="57">
+      <c r="M6" s="59">
         <v>3.23</v>
       </c>
-      <c r="N6" s="63">
+      <c r="N6" s="60">
         <v>2.66</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="65">
         <v>0.19</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="61">
         <v>-6.84</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="62">
         <v>-8.75</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="53">
         <v>-5.51</v>
       </c>
-      <c r="S6" s="64">
+      <c r="S6" s="54">
         <v>-5.32</v>
       </c>
-      <c r="T6" s="65">
-        <v>-18.06</v>
+      <c r="T6" s="63">
+        <v>-21.67</v>
       </c>
     </row>
     <row r="7">
@@ -2224,7 +2224,7 @@
       <c r="C7" t="str">
         <v>002542</v>
       </c>
-      <c r="D7" s="69" t="str">
+      <c r="D7" s="68" t="str">
         <v>净买: 684.27万</v>
       </c>
       <c r="E7">
@@ -2239,16 +2239,16 @@
       <c r="H7">
         <v>-4.24</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="69">
         <v>-4.42</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="70">
         <v>-7.52</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="71">
         <v>-10.18</v>
       </c>
-      <c r="L7" s="67">
+      <c r="L7" s="66">
         <v>-9.29</v>
       </c>
       <c r="M7" t="str"/>
@@ -2258,7 +2258,7 @@
       <c r="Q7" t="str"/>
       <c r="R7" t="str"/>
       <c r="S7" t="str"/>
-      <c r="T7" s="68">
+      <c r="T7" s="67">
         <v>-9.29</v>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="81">
+      <c r="I9" s="73">
         <v>33.33</v>
       </c>
       <c r="J9" s="82">
@@ -2336,25 +2336,25 @@
       <c r="M9" s="83">
         <v>60</v>
       </c>
-      <c r="N9" s="75">
+      <c r="N9" s="78">
         <v>60</v>
       </c>
-      <c r="O9" s="72">
+      <c r="O9" s="75">
         <v>60</v>
       </c>
-      <c r="P9" s="78">
+      <c r="P9" s="79">
         <v>40</v>
       </c>
-      <c r="Q9" s="73">
+      <c r="Q9" s="81">
         <v>40</v>
       </c>
-      <c r="R9" s="80">
+      <c r="R9" s="76">
         <v>40</v>
       </c>
-      <c r="S9" s="79">
+      <c r="S9" s="72">
         <v>40</v>
       </c>
-      <c r="T9" s="76">
+      <c r="T9" s="80">
         <v>33.33</v>
       </c>
     </row>
@@ -2372,38 +2372,38 @@
       <c r="I10" s="94">
         <v>3.33</v>
       </c>
-      <c r="J10" s="88">
+      <c r="J10" s="86">
         <v>8.09</v>
       </c>
-      <c r="K10" s="86">
+      <c r="K10" s="87">
         <v>3.35</v>
       </c>
-      <c r="L10" s="95">
+      <c r="L10" s="88">
         <v>5.78</v>
       </c>
-      <c r="M10" s="84">
+      <c r="M10" s="91">
         <v>6.71</v>
       </c>
-      <c r="N10" s="85">
+      <c r="N10" s="84">
         <v>8.47</v>
       </c>
-      <c r="O10" s="90">
+      <c r="O10" s="89">
         <v>6.91</v>
       </c>
-      <c r="P10" s="91">
+      <c r="P10" s="92">
         <v>0.8</v>
       </c>
-      <c r="Q10" s="92">
+      <c r="Q10" s="93">
         <v>1.32</v>
       </c>
-      <c r="R10" s="87">
+      <c r="R10" s="85">
         <v>1.04</v>
       </c>
-      <c r="S10" s="93">
+      <c r="S10" s="95">
         <v>0.65</v>
       </c>
-      <c r="T10" s="89">
-        <v>13.2</v>
+      <c r="T10" s="90">
+        <v>14.45</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/宁波解放南/index.xlsx
+++ b/youzi/宁波解放南/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="97">
+  <fills count="98">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -45,12 +45,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBCE3C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -63,18 +87,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBCE3C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -87,7 +99,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,6 +117,162 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -117,43 +285,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,55 +369,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -225,67 +465,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -297,31 +507,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -333,109 +519,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -447,97 +543,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77984"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -555,60 +591,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77984"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB82533"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF3BDC2"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="96">
+  <borders count="97">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -1285,7 +1298,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -1570,6 +1583,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="95" fillId="96" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="96" fillId="97" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -1914,7 +1930,7 @@
       <c r="C2" t="str">
         <v>600714</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="5" t="str">
         <v>净买: 735.89万</v>
       </c>
       <c r="E2">
@@ -1929,41 +1945,41 @@
       <c r="H2">
         <v>-4.48</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="6">
         <v>-5.78</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="2">
         <v>-1.54</v>
       </c>
       <c r="K2" s="7">
         <v>-11.35</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="8">
         <v>-11.2</v>
       </c>
       <c r="M2" s="12">
         <v>-13.91</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="13">
         <v>-13.47</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="9">
         <v>-10.47</v>
       </c>
-      <c r="P2" s="13">
+      <c r="P2" s="3">
         <v>-10.54</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="10">
         <v>-11.2</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="4">
         <v>-11.64</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="1">
         <v>-13.4</v>
       </c>
-      <c r="T2" s="5">
-        <v>38.21</v>
+      <c r="T2" s="11">
+        <v>36.09</v>
       </c>
     </row>
     <row r="3">
@@ -1976,7 +1992,7 @@
       <c r="C3" t="str">
         <v>688593</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="23" t="str">
         <v>净卖: -1079.85万</v>
       </c>
       <c r="E3">
@@ -1991,41 +2007,41 @@
       <c r="H3">
         <v>-0.06</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="14">
         <v>20.07</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="18">
         <v>35.34</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="24">
         <v>35.22</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="21">
         <v>46.33</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="19">
         <v>43.45</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="25">
         <v>51.86</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="26">
         <v>52.76</v>
       </c>
-      <c r="P3" s="26">
+      <c r="P3" s="15">
         <v>39.24</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="16">
         <v>39.12</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="17">
         <v>39.48</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="22">
         <v>35.58</v>
       </c>
-      <c r="T3" s="18">
-        <v>92.79</v>
+      <c r="T3" s="20">
+        <v>90.69</v>
       </c>
     </row>
     <row r="4">
@@ -2038,7 +2054,7 @@
       <c r="C4" t="str">
         <v>601500</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="28" t="str">
         <v>净买: 1639.55万</v>
       </c>
       <c r="E4">
@@ -2053,40 +2069,40 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="37">
         <v>10.09</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="32">
         <v>10.33</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="29">
         <v>8.22</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="30">
         <v>10.56</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="31">
         <v>13.15</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="33">
         <v>12.91</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="38">
         <v>12.44</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="35">
         <v>8.92</v>
       </c>
-      <c r="Q4" s="37">
+      <c r="Q4" s="36">
         <v>7.04</v>
       </c>
       <c r="R4" s="39">
         <v>9.15</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="27">
         <v>12.44</v>
       </c>
-      <c r="T4" s="35">
+      <c r="T4" s="34">
         <v>-0.94</v>
       </c>
     </row>
@@ -2100,7 +2116,7 @@
       <c r="C5" t="str">
         <v>600337</v>
       </c>
-      <c r="D5" s="43" t="str">
+      <c r="D5" s="48" t="str">
         <v>净买: 387.19万</v>
       </c>
       <c r="E5">
@@ -2115,41 +2131,41 @@
       <c r="H5">
         <v>9.92</v>
       </c>
-      <c r="I5" s="49">
+      <c r="I5" s="43">
         <v>0</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="49">
         <v>10.05</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="44">
         <v>-1.03</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="52">
         <v>-3.61</v>
       </c>
-      <c r="M5" s="50">
+      <c r="M5" s="45">
         <v>-12.37</v>
       </c>
-      <c r="N5" s="51">
+      <c r="N5" s="41">
         <v>-11.6</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="42">
         <v>-20.36</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="46">
         <v>-26.8</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="50">
         <v>-19.59</v>
       </c>
-      <c r="R5" s="41">
+      <c r="R5" s="51">
         <v>-26.29</v>
       </c>
-      <c r="S5" s="48">
+      <c r="S5" s="47">
         <v>-26.03</v>
       </c>
-      <c r="T5" s="42">
-        <v>-12.37</v>
+      <c r="T5" s="40">
+        <v>-12.89</v>
       </c>
     </row>
     <row r="6">
@@ -2180,38 +2196,38 @@
       <c r="I6" s="56">
         <v>0</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="54">
         <v>1.9</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="61">
         <v>-0.76</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="58">
         <v>1.9</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="62">
         <v>3.23</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="63">
         <v>2.66</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="59">
         <v>0.19</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="64">
         <v>-6.84</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="60">
         <v>-8.75</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="65">
         <v>-5.51</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="57">
         <v>-5.32</v>
       </c>
-      <c r="T6" s="63">
-        <v>-21.67</v>
+      <c r="T6" s="53">
+        <v>-23.76</v>
       </c>
     </row>
     <row r="7">
@@ -2219,12 +2235,12 @@
         <v>2026-04-14</v>
       </c>
       <c r="B7" t="str">
-        <v>中化岩土</v>
+        <v>*ST中岩</v>
       </c>
       <c r="C7" t="str">
         <v>002542</v>
       </c>
-      <c r="D7" s="68" t="str">
+      <c r="D7" s="71" t="str">
         <v>净买: 684.27万</v>
       </c>
       <c r="E7">
@@ -2239,27 +2255,29 @@
       <c r="H7">
         <v>-4.24</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="72">
         <v>-4.42</v>
       </c>
-      <c r="J7" s="70">
+      <c r="J7" s="66">
         <v>-7.52</v>
       </c>
-      <c r="K7" s="71">
+      <c r="K7" s="67">
         <v>-10.18</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="68">
         <v>-9.29</v>
       </c>
-      <c r="M7" t="str"/>
+      <c r="M7" s="69">
+        <v>-13.27</v>
+      </c>
       <c r="N7" t="str"/>
       <c r="O7" t="str"/>
       <c r="P7" t="str"/>
       <c r="Q7" t="str"/>
       <c r="R7" t="str"/>
       <c r="S7" t="str"/>
-      <c r="T7" s="67">
-        <v>-9.29</v>
+      <c r="T7" s="70">
+        <v>-13.27</v>
       </c>
     </row>
     <row r="8">
@@ -2286,7 +2304,7 @@
         <v>6</v>
       </c>
       <c r="M8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>5</v>
@@ -2321,40 +2339,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="73">
+      <c r="I9" s="79">
         <v>33.33</v>
       </c>
-      <c r="J9" s="82">
+      <c r="J9" s="74">
         <v>66.67</v>
       </c>
       <c r="K9" s="77">
         <v>33.33</v>
       </c>
-      <c r="L9" s="74">
+      <c r="L9" s="80">
         <v>50</v>
       </c>
-      <c r="M9" s="83">
+      <c r="M9" s="75">
+        <v>50</v>
+      </c>
+      <c r="N9" s="84">
         <v>60</v>
       </c>
-      <c r="N9" s="78">
+      <c r="O9" s="78">
         <v>60</v>
       </c>
-      <c r="O9" s="75">
-        <v>60</v>
-      </c>
-      <c r="P9" s="79">
+      <c r="P9" s="81">
         <v>40</v>
       </c>
-      <c r="Q9" s="81">
+      <c r="Q9" s="73">
         <v>40</v>
       </c>
-      <c r="R9" s="76">
+      <c r="R9" s="82">
         <v>40</v>
       </c>
-      <c r="S9" s="72">
+      <c r="S9" s="76">
         <v>40</v>
       </c>
-      <c r="T9" s="80">
+      <c r="T9" s="83">
         <v>33.33</v>
       </c>
     </row>
@@ -2369,41 +2387,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="94">
+      <c r="I10" s="93">
         <v>3.33</v>
       </c>
-      <c r="J10" s="86">
+      <c r="J10" s="94">
         <v>8.09</v>
       </c>
-      <c r="K10" s="87">
+      <c r="K10" s="85">
         <v>3.35</v>
       </c>
-      <c r="L10" s="88">
+      <c r="L10" s="95">
         <v>5.78</v>
       </c>
-      <c r="M10" s="91">
-        <v>6.71</v>
-      </c>
-      <c r="N10" s="84">
+      <c r="M10" s="86">
+        <v>3.38</v>
+      </c>
+      <c r="N10" s="87">
         <v>8.47</v>
       </c>
-      <c r="O10" s="89">
+      <c r="O10" s="88">
         <v>6.91</v>
       </c>
-      <c r="P10" s="92">
+      <c r="P10" s="89">
         <v>0.8</v>
       </c>
-      <c r="Q10" s="93">
+      <c r="Q10" s="90">
         <v>1.32</v>
       </c>
-      <c r="R10" s="85">
+      <c r="R10" s="91">
         <v>1.04</v>
       </c>
-      <c r="S10" s="95">
+      <c r="S10" s="96">
         <v>0.65</v>
       </c>
-      <c r="T10" s="90">
-        <v>14.45</v>
+      <c r="T10" s="92">
+        <v>12.65</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/宁波解放南/index.xlsx
+++ b/youzi/宁波解放南/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="98">
+  <fills count="101">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,12 +39,66 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBCE3C5"/>
         <bgColor/>
       </patternFill>
@@ -57,36 +111,324 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -99,19 +441,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE77984"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,492 +609,51 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77984"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF3BDC2"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="97">
+  <borders count="100">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -1298,7 +1337,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="100">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -1586,6 +1625,15 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="96" fillId="97" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="97" fillId="98" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="98" fillId="99" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="99" fillId="100" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -1930,7 +1978,7 @@
       <c r="C2" t="str">
         <v>600714</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="1" t="str">
         <v>净买: 735.89万</v>
       </c>
       <c r="E2">
@@ -1945,41 +1993,41 @@
       <c r="H2">
         <v>-4.48</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="2">
         <v>-5.78</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="11">
         <v>-1.54</v>
       </c>
       <c r="K2" s="7">
         <v>-11.35</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="3">
         <v>-11.2</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="8">
         <v>-13.91</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="9">
         <v>-13.47</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="6">
         <v>-10.47</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="10">
         <v>-10.54</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="4">
         <v>-11.2</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="5">
         <v>-11.64</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="12">
         <v>-13.4</v>
       </c>
-      <c r="T2" s="11">
-        <v>36.09</v>
+      <c r="T2" s="13">
+        <v>32.14</v>
       </c>
     </row>
     <row r="3">
@@ -1992,7 +2040,7 @@
       <c r="C3" t="str">
         <v>688593</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="24" t="str">
         <v>净卖: -1079.85万</v>
       </c>
       <c r="E3">
@@ -2007,41 +2055,41 @@
       <c r="H3">
         <v>-0.06</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="22">
         <v>20.07</v>
       </c>
       <c r="J3" s="18">
         <v>35.34</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="19">
         <v>35.22</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="23">
         <v>46.33</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="25">
         <v>43.45</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="26">
         <v>51.86</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="20">
         <v>52.76</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="14">
         <v>39.24</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="15">
         <v>39.12</v>
       </c>
-      <c r="R3" s="17">
+      <c r="R3" s="16">
         <v>39.48</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="21">
         <v>35.58</v>
       </c>
-      <c r="T3" s="20">
-        <v>90.69</v>
+      <c r="T3" s="17">
+        <v>87.92</v>
       </c>
     </row>
     <row r="4">
@@ -2054,7 +2102,7 @@
       <c r="C4" t="str">
         <v>601500</v>
       </c>
-      <c r="D4" s="28" t="str">
+      <c r="D4" s="37" t="str">
         <v>净买: 1639.55万</v>
       </c>
       <c r="E4">
@@ -2069,41 +2117,41 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="38">
         <v>10.09</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="39">
         <v>10.33</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="30">
         <v>8.22</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="28">
         <v>10.56</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="27">
         <v>13.15</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="29">
         <v>12.91</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="31">
         <v>12.44</v>
       </c>
       <c r="P4" s="35">
         <v>8.92</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="32">
         <v>7.04</v>
       </c>
-      <c r="R4" s="39">
+      <c r="R4" s="33">
         <v>9.15</v>
       </c>
-      <c r="S4" s="27">
+      <c r="S4" s="36">
         <v>12.44</v>
       </c>
       <c r="T4" s="34">
-        <v>-0.94</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
@@ -2116,7 +2164,7 @@
       <c r="C5" t="str">
         <v>600337</v>
       </c>
-      <c r="D5" s="48" t="str">
+      <c r="D5" s="51" t="str">
         <v>净买: 387.19万</v>
       </c>
       <c r="E5">
@@ -2131,41 +2179,41 @@
       <c r="H5">
         <v>9.92</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="42">
         <v>0</v>
       </c>
-      <c r="J5" s="49">
+      <c r="J5" s="46">
         <v>10.05</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="47">
         <v>-1.03</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="48">
         <v>-3.61</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="44">
         <v>-12.37</v>
       </c>
-      <c r="N5" s="41">
+      <c r="N5" s="52">
         <v>-11.6</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="45">
         <v>-20.36</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="49">
         <v>-26.8</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="43">
         <v>-19.59</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="40">
         <v>-26.29</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="41">
         <v>-26.03</v>
       </c>
-      <c r="T5" s="40">
-        <v>-12.89</v>
+      <c r="T5" s="50">
+        <v>-19.33</v>
       </c>
     </row>
     <row r="6">
@@ -2178,7 +2226,7 @@
       <c r="C6" t="str">
         <v>603718</v>
       </c>
-      <c r="D6" s="55" t="str">
+      <c r="D6" s="60" t="str">
         <v>净卖: -161.85万</v>
       </c>
       <c r="E6">
@@ -2193,41 +2241,41 @@
       <c r="H6">
         <v>-9.93</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="54">
         <v>0</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="65">
         <v>1.9</v>
       </c>
       <c r="K6" s="61">
         <v>-0.76</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="56">
         <v>1.9</v>
       </c>
       <c r="M6" s="62">
         <v>3.23</v>
       </c>
-      <c r="N6" s="63">
+      <c r="N6" s="53">
         <v>2.66</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="57">
         <v>0.19</v>
       </c>
-      <c r="P6" s="64">
+      <c r="P6" s="58">
         <v>-6.84</v>
       </c>
-      <c r="Q6" s="60">
+      <c r="Q6" s="59">
         <v>-8.75</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="63">
         <v>-5.51</v>
       </c>
-      <c r="S6" s="57">
+      <c r="S6" s="55">
         <v>-5.32</v>
       </c>
-      <c r="T6" s="53">
-        <v>-23.76</v>
+      <c r="T6" s="64">
+        <v>-24.71</v>
       </c>
     </row>
     <row r="7">
@@ -2255,29 +2303,35 @@
       <c r="H7">
         <v>-4.24</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="69">
         <v>-4.42</v>
       </c>
-      <c r="J7" s="66">
+      <c r="J7" s="74">
         <v>-7.52</v>
       </c>
-      <c r="K7" s="67">
+      <c r="K7" s="75">
         <v>-10.18</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="70">
         <v>-9.29</v>
       </c>
-      <c r="M7" s="69">
+      <c r="M7" s="66">
         <v>-13.27</v>
       </c>
-      <c r="N7" t="str"/>
-      <c r="O7" t="str"/>
-      <c r="P7" t="str"/>
+      <c r="N7" s="72">
+        <v>-17.7</v>
+      </c>
+      <c r="O7" s="67">
+        <v>-16.81</v>
+      </c>
+      <c r="P7" s="73">
+        <v>-20.8</v>
+      </c>
       <c r="Q7" t="str"/>
       <c r="R7" t="str"/>
       <c r="S7" t="str"/>
-      <c r="T7" s="70">
-        <v>-13.27</v>
+      <c r="T7" s="68">
+        <v>-20.8</v>
       </c>
     </row>
     <row r="8">
@@ -2307,13 +2361,13 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q8">
         <v>5</v>
@@ -2339,41 +2393,41 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="79">
+      <c r="I9" s="85">
         <v>33.33</v>
       </c>
-      <c r="J9" s="74">
+      <c r="J9" s="78">
         <v>66.67</v>
       </c>
-      <c r="K9" s="77">
+      <c r="K9" s="79">
         <v>33.33</v>
       </c>
       <c r="L9" s="80">
         <v>50</v>
       </c>
-      <c r="M9" s="75">
+      <c r="M9" s="83">
         <v>50</v>
       </c>
-      <c r="N9" s="84">
-        <v>60</v>
-      </c>
-      <c r="O9" s="78">
-        <v>60</v>
-      </c>
-      <c r="P9" s="81">
+      <c r="N9" s="81">
+        <v>50</v>
+      </c>
+      <c r="O9" s="86">
+        <v>50</v>
+      </c>
+      <c r="P9" s="76">
+        <v>33.33</v>
+      </c>
+      <c r="Q9" s="82">
         <v>40</v>
       </c>
-      <c r="Q9" s="73">
+      <c r="R9" s="77">
         <v>40</v>
       </c>
-      <c r="R9" s="82">
+      <c r="S9" s="87">
         <v>40</v>
       </c>
-      <c r="S9" s="76">
-        <v>40</v>
-      </c>
-      <c r="T9" s="83">
-        <v>33.33</v>
+      <c r="T9" s="84">
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -2387,41 +2441,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="93">
+      <c r="I10" s="88">
         <v>3.33</v>
       </c>
       <c r="J10" s="94">
         <v>8.09</v>
       </c>
-      <c r="K10" s="85">
+      <c r="K10" s="91">
         <v>3.35</v>
       </c>
-      <c r="L10" s="95">
+      <c r="L10" s="92">
         <v>5.78</v>
       </c>
-      <c r="M10" s="86">
+      <c r="M10" s="89">
         <v>3.38</v>
       </c>
-      <c r="N10" s="87">
-        <v>8.47</v>
-      </c>
-      <c r="O10" s="88">
-        <v>6.91</v>
-      </c>
-      <c r="P10" s="89">
-        <v>0.8</v>
-      </c>
-      <c r="Q10" s="90">
+      <c r="N10" s="95">
+        <v>4.11</v>
+      </c>
+      <c r="O10" s="96">
+        <v>2.96</v>
+      </c>
+      <c r="P10" s="97">
+        <v>-2.8</v>
+      </c>
+      <c r="Q10" s="93">
         <v>1.32</v>
       </c>
-      <c r="R10" s="91">
+      <c r="R10" s="90">
         <v>1.04</v>
       </c>
-      <c r="S10" s="96">
+      <c r="S10" s="99">
         <v>0.65</v>
       </c>
-      <c r="T10" s="92">
-        <v>12.65</v>
+      <c r="T10" s="98">
+        <v>9.32</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/宁波解放南/index.xlsx
+++ b/youzi/宁波解放南/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="101">
+  <fills count="102">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,6 +39,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBCE3C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -63,6 +117,180 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B3B9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -93,36 +321,312 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBCE3C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB82533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -133,506 +637,15 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77984"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="100">
+  <borders count="101">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -1337,7 +1350,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="101">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -1634,6 +1647,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="99" fillId="100" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="100" fillId="101" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -1978,7 +1994,7 @@
       <c r="C2" t="str">
         <v>600714</v>
       </c>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="10" t="str">
         <v>净买: 735.89万</v>
       </c>
       <c r="E2">
@@ -1993,41 +2009,41 @@
       <c r="H2">
         <v>-4.48</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="11">
         <v>-5.78</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="2">
         <v>-1.54</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="5">
         <v>-11.35</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="6">
         <v>-11.2</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2" s="12">
         <v>-13.91</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="3">
         <v>-13.47</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="13">
         <v>-10.47</v>
       </c>
-      <c r="P2" s="10">
+      <c r="P2" s="7">
         <v>-10.54</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="1">
         <v>-11.2</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="4">
         <v>-11.64</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="8">
         <v>-13.4</v>
       </c>
-      <c r="T2" s="13">
-        <v>32.14</v>
+      <c r="T2" s="9">
+        <v>34.04</v>
       </c>
     </row>
     <row r="3">
@@ -2040,7 +2056,7 @@
       <c r="C3" t="str">
         <v>688593</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="14" t="str">
         <v>净卖: -1079.85万</v>
       </c>
       <c r="E3">
@@ -2055,41 +2071,41 @@
       <c r="H3">
         <v>-0.06</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="21">
         <v>20.07</v>
       </c>
-      <c r="J3" s="18">
+      <c r="J3" s="22">
         <v>35.34</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="26">
         <v>35.22</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="16">
         <v>46.33</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="17">
         <v>43.45</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="23">
         <v>51.86</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="15">
         <v>52.76</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="24">
         <v>39.24</v>
       </c>
-      <c r="Q3" s="15">
+      <c r="Q3" s="18">
         <v>39.12</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="19">
         <v>39.48</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="20">
         <v>35.58</v>
       </c>
-      <c r="T3" s="17">
-        <v>87.92</v>
+      <c r="T3" s="25">
+        <v>105.89</v>
       </c>
     </row>
     <row r="4">
@@ -2102,7 +2118,7 @@
       <c r="C4" t="str">
         <v>601500</v>
       </c>
-      <c r="D4" s="37" t="str">
+      <c r="D4" s="39" t="str">
         <v>净买: 1639.55万</v>
       </c>
       <c r="E4">
@@ -2117,41 +2133,41 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="27">
         <v>10.09</v>
       </c>
-      <c r="J4" s="39">
+      <c r="J4" s="28">
         <v>10.33</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="31">
         <v>8.22</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="32">
         <v>10.56</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="33">
         <v>13.15</v>
       </c>
       <c r="N4" s="29">
         <v>12.91</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="37">
         <v>12.44</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="38">
         <v>8.92</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="30">
         <v>7.04</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="34">
         <v>9.15</v>
       </c>
-      <c r="S4" s="36">
+      <c r="S4" s="35">
         <v>12.44</v>
       </c>
-      <c r="T4" s="34">
-        <v>0.7</v>
+      <c r="T4" s="36">
+        <v>1.88</v>
       </c>
     </row>
     <row r="5">
@@ -2164,7 +2180,7 @@
       <c r="C5" t="str">
         <v>600337</v>
       </c>
-      <c r="D5" s="51" t="str">
+      <c r="D5" s="52" t="str">
         <v>净买: 387.19万</v>
       </c>
       <c r="E5">
@@ -2179,41 +2195,41 @@
       <c r="H5">
         <v>9.92</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="40">
         <v>0</v>
       </c>
-      <c r="J5" s="46">
+      <c r="J5" s="48">
         <v>10.05</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="41">
         <v>-1.03</v>
       </c>
-      <c r="L5" s="48">
+      <c r="L5" s="42">
         <v>-3.61</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="43">
         <v>-12.37</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="44">
         <v>-11.6</v>
       </c>
       <c r="O5" s="45">
         <v>-20.36</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="46">
         <v>-26.8</v>
       </c>
-      <c r="Q5" s="43">
+      <c r="Q5" s="49">
         <v>-19.59</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="51">
         <v>-26.29</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="47">
         <v>-26.03</v>
       </c>
       <c r="T5" s="50">
-        <v>-19.33</v>
+        <v>-25.52</v>
       </c>
     </row>
     <row r="6">
@@ -2226,7 +2242,7 @@
       <c r="C6" t="str">
         <v>603718</v>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D6" s="62" t="str">
         <v>净卖: -161.85万</v>
       </c>
       <c r="E6">
@@ -2241,41 +2257,41 @@
       <c r="H6">
         <v>-9.93</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="57">
         <v>0</v>
       </c>
-      <c r="J6" s="65">
+      <c r="J6" s="59">
         <v>1.9</v>
       </c>
-      <c r="K6" s="61">
+      <c r="K6" s="53">
         <v>-0.76</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="54">
         <v>1.9</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="63">
         <v>3.23</v>
       </c>
-      <c r="N6" s="53">
+      <c r="N6" s="60">
         <v>2.66</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="61">
         <v>0.19</v>
       </c>
       <c r="P6" s="58">
         <v>-6.84</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="64">
         <v>-8.75</v>
       </c>
-      <c r="R6" s="63">
+      <c r="R6" s="55">
         <v>-5.51</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="65">
         <v>-5.32</v>
       </c>
-      <c r="T6" s="64">
-        <v>-24.71</v>
+      <c r="T6" s="56">
+        <v>-26.24</v>
       </c>
     </row>
     <row r="7">
@@ -2303,35 +2319,37 @@
       <c r="H7">
         <v>-4.24</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="70">
         <v>-4.42</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="76">
         <v>-7.52</v>
       </c>
-      <c r="K7" s="75">
+      <c r="K7" s="69">
         <v>-10.18</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="66">
         <v>-9.29</v>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="72">
         <v>-13.27</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="73">
         <v>-17.7</v>
       </c>
-      <c r="O7" s="67">
+      <c r="O7" s="74">
         <v>-16.81</v>
       </c>
-      <c r="P7" s="73">
+      <c r="P7" s="75">
         <v>-20.8</v>
       </c>
-      <c r="Q7" t="str"/>
+      <c r="Q7" s="67">
+        <v>-19.47</v>
+      </c>
       <c r="R7" t="str"/>
       <c r="S7" t="str"/>
       <c r="T7" s="68">
-        <v>-20.8</v>
+        <v>-19.47</v>
       </c>
     </row>
     <row r="8">
@@ -2370,7 +2388,7 @@
         <v>6</v>
       </c>
       <c r="Q8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R8">
         <v>5</v>
@@ -2393,40 +2411,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="85">
+      <c r="I9" s="78">
         <v>33.33</v>
       </c>
-      <c r="J9" s="78">
+      <c r="J9" s="79">
         <v>66.67</v>
       </c>
-      <c r="K9" s="79">
+      <c r="K9" s="87">
         <v>33.33</v>
       </c>
-      <c r="L9" s="80">
+      <c r="L9" s="82">
         <v>50</v>
       </c>
-      <c r="M9" s="83">
+      <c r="M9" s="88">
         <v>50</v>
       </c>
-      <c r="N9" s="81">
+      <c r="N9" s="83">
         <v>50</v>
       </c>
-      <c r="O9" s="86">
+      <c r="O9" s="80">
         <v>50</v>
       </c>
-      <c r="P9" s="76">
+      <c r="P9" s="84">
         <v>33.33</v>
       </c>
-      <c r="Q9" s="82">
+      <c r="Q9" s="81">
+        <v>33.33</v>
+      </c>
+      <c r="R9" s="85">
         <v>40</v>
       </c>
-      <c r="R9" s="77">
+      <c r="S9" s="77">
         <v>40</v>
       </c>
-      <c r="S9" s="87">
-        <v>40</v>
-      </c>
-      <c r="T9" s="84">
+      <c r="T9" s="86">
         <v>50</v>
       </c>
     </row>
@@ -2441,41 +2459,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="88">
+      <c r="I10" s="93">
         <v>3.33</v>
       </c>
-      <c r="J10" s="94">
+      <c r="J10" s="100">
         <v>8.09</v>
       </c>
-      <c r="K10" s="91">
+      <c r="K10" s="94">
         <v>3.35</v>
       </c>
-      <c r="L10" s="92">
+      <c r="L10" s="95">
         <v>5.78</v>
       </c>
       <c r="M10" s="89">
         <v>3.38</v>
       </c>
-      <c r="N10" s="95">
+      <c r="N10" s="92">
         <v>4.11</v>
       </c>
-      <c r="O10" s="96">
+      <c r="O10" s="90">
         <v>2.96</v>
       </c>
-      <c r="P10" s="97">
+      <c r="P10" s="91">
         <v>-2.8</v>
       </c>
-      <c r="Q10" s="93">
-        <v>1.32</v>
-      </c>
-      <c r="R10" s="90">
+      <c r="Q10" s="97">
+        <v>-2.14</v>
+      </c>
+      <c r="R10" s="96">
         <v>1.04</v>
       </c>
-      <c r="S10" s="99">
+      <c r="S10" s="98">
         <v>0.65</v>
       </c>
-      <c r="T10" s="98">
-        <v>9.32</v>
+      <c r="T10" s="99">
+        <v>11.76</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/宁波解放南/index.xlsx
+++ b/youzi/宁波解放南/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="102">
+  <fills count="103">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,12 +39,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBCE3C5"/>
         <bgColor/>
       </patternFill>
@@ -93,13 +123,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D9DC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,18 +279,318 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87C86"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF7F7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A042"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDEF1E2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF40B15A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22923D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BDC2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -141,451 +609,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228F3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B3B9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEF1E2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A042"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF7F7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87C86"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF40B15A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC22938"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF228F3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF26A243"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -595,50 +643,15 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BDC2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="101">
+  <borders count="102">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -1350,7 +1363,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="102">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -1650,6 +1663,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="100" fillId="101" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="101" fillId="102" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -1994,7 +2010,7 @@
       <c r="C2" t="str">
         <v>600714</v>
       </c>
-      <c r="D2" s="10" t="str">
+      <c r="D2" s="5" t="str">
         <v>净买: 735.89万</v>
       </c>
       <c r="E2">
@@ -2009,41 +2025,41 @@
       <c r="H2">
         <v>-4.48</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="6">
         <v>-5.78</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="7">
         <v>-1.54</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="2">
         <v>-11.35</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="3">
         <v>-11.2</v>
       </c>
       <c r="M2" s="12">
         <v>-13.91</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="8">
         <v>-13.47</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="4">
         <v>-10.47</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="11">
         <v>-10.54</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="9">
         <v>-11.2</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="10">
         <v>-11.64</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="13">
         <v>-13.4</v>
       </c>
-      <c r="T2" s="9">
-        <v>34.04</v>
+      <c r="T2" s="1">
+        <v>33.67</v>
       </c>
     </row>
     <row r="3">
@@ -2056,7 +2072,7 @@
       <c r="C3" t="str">
         <v>688593</v>
       </c>
-      <c r="D3" s="14" t="str">
+      <c r="D3" s="19" t="str">
         <v>净卖: -1079.85万</v>
       </c>
       <c r="E3">
@@ -2071,41 +2087,41 @@
       <c r="H3">
         <v>-0.06</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="16">
         <v>20.07</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="20">
         <v>35.34</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="17">
         <v>35.22</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="22">
         <v>46.33</v>
       </c>
-      <c r="M3" s="17">
+      <c r="M3" s="25">
         <v>43.45</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="26">
         <v>51.86</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="14">
         <v>52.76</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="21">
         <v>39.24</v>
       </c>
       <c r="Q3" s="18">
         <v>39.12</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="15">
         <v>39.48</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="23">
         <v>35.58</v>
       </c>
-      <c r="T3" s="25">
-        <v>105.89</v>
+      <c r="T3" s="24">
+        <v>85.34</v>
       </c>
     </row>
     <row r="4">
@@ -2118,7 +2134,7 @@
       <c r="C4" t="str">
         <v>601500</v>
       </c>
-      <c r="D4" s="39" t="str">
+      <c r="D4" s="27" t="str">
         <v>净买: 1639.55万</v>
       </c>
       <c r="E4">
@@ -2133,41 +2149,41 @@
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="28">
         <v>10.09</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="31">
         <v>10.33</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="33">
         <v>8.22</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="38">
         <v>10.56</v>
       </c>
-      <c r="M4" s="33">
+      <c r="M4" s="29">
         <v>13.15</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="32">
         <v>12.91</v>
       </c>
-      <c r="O4" s="37">
+      <c r="O4" s="34">
         <v>12.44</v>
       </c>
-      <c r="P4" s="38">
+      <c r="P4" s="39">
         <v>8.92</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="35">
         <v>7.04</v>
       </c>
-      <c r="R4" s="34">
+      <c r="R4" s="30">
         <v>9.15</v>
       </c>
-      <c r="S4" s="35">
+      <c r="S4" s="36">
         <v>12.44</v>
       </c>
-      <c r="T4" s="36">
-        <v>1.88</v>
+      <c r="T4" s="37">
+        <v>0.94</v>
       </c>
     </row>
     <row r="5">
@@ -2180,7 +2196,7 @@
       <c r="C5" t="str">
         <v>600337</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="41" t="str">
         <v>净买: 387.19万</v>
       </c>
       <c r="E5">
@@ -2195,41 +2211,41 @@
       <c r="H5">
         <v>9.92</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="51">
         <v>0</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="42">
         <v>10.05</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="47">
         <v>-1.03</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="43">
         <v>-3.61</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="48">
         <v>-12.37</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="49">
         <v>-11.6</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="52">
         <v>-20.36</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="50">
         <v>-26.8</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="40">
         <v>-19.59</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="44">
         <v>-26.29</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="45">
         <v>-26.03</v>
       </c>
-      <c r="T5" s="50">
-        <v>-25.52</v>
+      <c r="T5" s="46">
+        <v>-29.9</v>
       </c>
     </row>
     <row r="6">
@@ -2242,7 +2258,7 @@
       <c r="C6" t="str">
         <v>603718</v>
       </c>
-      <c r="D6" s="62" t="str">
+      <c r="D6" s="64" t="str">
         <v>净卖: -161.85万</v>
       </c>
       <c r="E6">
@@ -2257,41 +2273,41 @@
       <c r="H6">
         <v>-9.93</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="59">
         <v>0</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="60">
         <v>1.9</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="65">
         <v>-0.76</v>
       </c>
-      <c r="L6" s="54">
+      <c r="L6" s="53">
         <v>1.9</v>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="54">
         <v>3.23</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="61">
         <v>2.66</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="55">
         <v>0.19</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="56">
         <v>-6.84</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="57">
         <v>-8.75</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="62">
         <v>-5.51</v>
       </c>
-      <c r="S6" s="65">
+      <c r="S6" s="58">
         <v>-5.32</v>
       </c>
-      <c r="T6" s="56">
-        <v>-26.24</v>
+      <c r="T6" s="63">
+        <v>-26.81</v>
       </c>
     </row>
     <row r="7">
@@ -2304,7 +2320,7 @@
       <c r="C7" t="str">
         <v>002542</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="67" t="str">
         <v>净买: 684.27万</v>
       </c>
       <c r="E7">
@@ -2319,37 +2335,39 @@
       <c r="H7">
         <v>-4.24</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="74">
         <v>-4.42</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="75">
         <v>-7.52</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="76">
         <v>-10.18</v>
       </c>
-      <c r="L7" s="66">
+      <c r="L7" s="71">
         <v>-9.29</v>
       </c>
-      <c r="M7" s="72">
+      <c r="M7" s="77">
         <v>-13.27</v>
       </c>
-      <c r="N7" s="73">
+      <c r="N7" s="66">
         <v>-17.7</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="68">
         <v>-16.81</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="69">
         <v>-20.8</v>
       </c>
-      <c r="Q7" s="67">
+      <c r="Q7" s="72">
         <v>-19.47</v>
       </c>
-      <c r="R7" t="str"/>
+      <c r="R7" s="73">
+        <v>-21.24</v>
+      </c>
       <c r="S7" t="str"/>
-      <c r="T7" s="68">
-        <v>-19.47</v>
+      <c r="T7" s="70">
+        <v>-21.24</v>
       </c>
     </row>
     <row r="8">
@@ -2391,7 +2409,7 @@
         <v>6</v>
       </c>
       <c r="R8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S8">
         <v>5</v>
@@ -2411,40 +2429,40 @@
       <c r="F9" t="str"/>
       <c r="G9" t="str"/>
       <c r="H9" t="str"/>
-      <c r="I9" s="78">
+      <c r="I9" s="83">
         <v>33.33</v>
       </c>
-      <c r="J9" s="79">
+      <c r="J9" s="84">
         <v>66.67</v>
       </c>
-      <c r="K9" s="87">
+      <c r="K9" s="89">
         <v>33.33</v>
       </c>
-      <c r="L9" s="82">
+      <c r="L9" s="85">
         <v>50</v>
       </c>
-      <c r="M9" s="88">
+      <c r="M9" s="81">
         <v>50</v>
       </c>
-      <c r="N9" s="83">
+      <c r="N9" s="82">
         <v>50</v>
       </c>
-      <c r="O9" s="80">
+      <c r="O9" s="78">
         <v>50</v>
       </c>
-      <c r="P9" s="84">
+      <c r="P9" s="86">
         <v>33.33</v>
       </c>
-      <c r="Q9" s="81">
+      <c r="Q9" s="79">
         <v>33.33</v>
       </c>
-      <c r="R9" s="85">
+      <c r="R9" s="87">
+        <v>33.33</v>
+      </c>
+      <c r="S9" s="80">
         <v>40</v>
       </c>
-      <c r="S9" s="77">
-        <v>40</v>
-      </c>
-      <c r="T9" s="86">
+      <c r="T9" s="88">
         <v>50</v>
       </c>
     </row>
@@ -2459,41 +2477,41 @@
       <c r="F10" t="str"/>
       <c r="G10" t="str"/>
       <c r="H10" t="str"/>
-      <c r="I10" s="93">
+      <c r="I10" s="101">
         <v>3.33</v>
       </c>
-      <c r="J10" s="100">
+      <c r="J10" s="95">
         <v>8.09</v>
       </c>
-      <c r="K10" s="94">
+      <c r="K10" s="90">
         <v>3.35</v>
       </c>
-      <c r="L10" s="95">
+      <c r="L10" s="93">
         <v>5.78</v>
       </c>
-      <c r="M10" s="89">
+      <c r="M10" s="96">
         <v>3.38</v>
       </c>
-      <c r="N10" s="92">
+      <c r="N10" s="94">
         <v>4.11</v>
       </c>
-      <c r="O10" s="90">
+      <c r="O10" s="99">
         <v>2.96</v>
       </c>
-      <c r="P10" s="91">
+      <c r="P10" s="97">
         <v>-2.8</v>
       </c>
-      <c r="Q10" s="97">
+      <c r="Q10" s="100">
         <v>-2.14</v>
       </c>
-      <c r="R10" s="96">
-        <v>1.04</v>
-      </c>
-      <c r="S10" s="98">
+      <c r="R10" s="91">
+        <v>-2.68</v>
+      </c>
+      <c r="S10" s="92">
         <v>0.65</v>
       </c>
-      <c r="T10" s="99">
-        <v>11.76</v>
+      <c r="T10" s="98">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
